--- a/python-project.xlsx
+++ b/python-project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D92B08-43AF-4B6B-9B75-43CC73AA29A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F56E54A0-F82F-40C7-9DFA-BB489DC80F28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -214,7 +214,13 @@
     <t>Neutral</t>
   </si>
   <si>
-    <t>tired</t>
+    <t>I felt tired.</t>
+  </si>
+  <si>
+    <t>felt a bit tired.</t>
+  </si>
+  <si>
+    <t>It was Saturday so no classes.</t>
   </si>
 </sst>
 </file>
@@ -1128,47 +1134,87 @@
         <v>51</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46242</v>
+      </c>
+      <c r="B9" s="14">
+        <v>480</v>
+      </c>
+      <c r="C9" s="14">
+        <v>30</v>
+      </c>
+      <c r="D9" s="14">
+        <v>90</v>
+      </c>
+      <c r="E9" s="14">
+        <v>60</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14">
+        <v>120</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46243</v>
+      </c>
+      <c r="B10" s="14">
+        <v>480</v>
+      </c>
+      <c r="C10" s="14">
+        <v>30</v>
+      </c>
+      <c r="D10" s="14">
+        <v>90</v>
+      </c>
+      <c r="E10" s="14">
+        <v>60</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14">
+        <v>120</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>660</v>
       </c>
       <c r="K10" s="16"/>
       <c r="L10" s="16"/>

--- a/python-project.xlsx
+++ b/python-project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F56E54A0-F82F-40C7-9DFA-BB489DC80F28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B901931-B3E7-439E-9A75-09E1AC4D7B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -221,6 +221,18 @@
   </si>
   <si>
     <t>It was Saturday so no classes.</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>It was Sunday.</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>It was a slow day.</t>
   </si>
 </sst>
 </file>
@@ -1216,35 +1228,69 @@
         <f t="shared" si="1"/>
         <v>660</v>
       </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+      <c r="K10" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46244</v>
+      </c>
+      <c r="B11" s="14">
+        <v>360</v>
+      </c>
+      <c r="C11" s="14">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14">
+        <v>120</v>
+      </c>
+      <c r="E11" s="14">
+        <v>45</v>
+      </c>
+      <c r="F11" s="14">
+        <v>300</v>
+      </c>
+      <c r="G11" s="14">
+        <v>5</v>
+      </c>
+      <c r="H11" s="14">
+        <v>60</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>885</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>555</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
+      <c r="A12" s="13">
+        <v>46245</v>
+      </c>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
@@ -1266,7 +1312,9 @@
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
+      <c r="A13" s="13">
+        <v>46246</v>
+      </c>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
@@ -1288,7 +1336,9 @@
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
+      <c r="A14" s="13">
+        <v>46247</v>
+      </c>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
@@ -1310,7 +1360,9 @@
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
+      <c r="A15" s="13">
+        <v>46248</v>
+      </c>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
@@ -1332,7 +1384,9 @@
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
+      <c r="A16" s="13">
+        <v>46249</v>
+      </c>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
@@ -1354,7 +1408,9 @@
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
+      <c r="A17" s="13">
+        <v>46250</v>
+      </c>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
@@ -1376,7 +1432,9 @@
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
+      <c r="A18" s="13">
+        <v>46251</v>
+      </c>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
@@ -1398,7 +1456,9 @@
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
+      <c r="A19" s="13">
+        <v>46252</v>
+      </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
@@ -1420,7 +1480,9 @@
       <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
+      <c r="A20" s="13">
+        <v>46253</v>
+      </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
@@ -1442,7 +1504,9 @@
       <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
+      <c r="A21" s="13">
+        <v>46254</v>
+      </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
       <c r="D21" s="14"/>
@@ -1464,7 +1528,9 @@
       <c r="N21" s="17"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
+      <c r="A22" s="13">
+        <v>46255</v>
+      </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
@@ -1486,7 +1552,9 @@
       <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
+      <c r="A23" s="13">
+        <v>46256</v>
+      </c>
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
       <c r="D23" s="14"/>
@@ -1508,7 +1576,9 @@
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
+      <c r="A24" s="13">
+        <v>46257</v>
+      </c>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
       <c r="D24" s="14"/>
@@ -1530,7 +1600,9 @@
       <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
+      <c r="A25" s="13">
+        <v>46258</v>
+      </c>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
       <c r="D25" s="14"/>
@@ -1552,7 +1624,9 @@
       <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
+      <c r="A26" s="13">
+        <v>46259</v>
+      </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
       <c r="D26" s="14"/>
@@ -1574,7 +1648,9 @@
       <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
+      <c r="A27" s="13">
+        <v>46260</v>
+      </c>
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
       <c r="D27" s="14"/>
@@ -1596,7 +1672,9 @@
       <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
+      <c r="A28" s="13">
+        <v>46261</v>
+      </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
       <c r="D28" s="14"/>
@@ -1618,7 +1696,9 @@
       <c r="N28" s="17"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
+      <c r="A29" s="13">
+        <v>46262</v>
+      </c>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
       <c r="D29" s="14"/>
@@ -1640,7 +1720,9 @@
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
+      <c r="A30" s="13">
+        <v>46263</v>
+      </c>
       <c r="B30" s="14"/>
       <c r="C30" s="14"/>
       <c r="D30" s="14"/>
@@ -1662,7 +1744,9 @@
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
+      <c r="A31" s="13">
+        <v>46264</v>
+      </c>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
@@ -1684,7 +1768,9 @@
       <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
+      <c r="A32" s="13">
+        <v>46266</v>
+      </c>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
@@ -1706,7 +1792,9 @@
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
+      <c r="A33" s="13">
+        <v>46267</v>
+      </c>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
       <c r="D33" s="14"/>

--- a/python-project.xlsx
+++ b/python-project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B901931-B3E7-439E-9A75-09E1AC4D7B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8CCFCF8-9715-4851-8C36-8FC66218B77C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -233,6 +233,12 @@
   </si>
   <si>
     <t>It was a slow day.</t>
+  </si>
+  <si>
+    <t>It was a good day.</t>
+  </si>
+  <si>
+    <t>It was Saturday.</t>
   </si>
 </sst>
 </file>
@@ -1291,485 +1297,925 @@
       <c r="A12" s="13">
         <v>46245</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="B12" s="14">
+        <v>360</v>
+      </c>
+      <c r="C12" s="14">
+        <v>45</v>
+      </c>
+      <c r="D12" s="14">
+        <v>120</v>
+      </c>
+      <c r="E12" s="14">
+        <v>30</v>
+      </c>
+      <c r="F12" s="14">
+        <v>300</v>
+      </c>
+      <c r="G12" s="14">
+        <v>5</v>
+      </c>
+      <c r="H12" s="14">
+        <v>60</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>915</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>525</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
         <v>46246</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="B13" s="14">
+        <v>360</v>
+      </c>
+      <c r="C13" s="14">
+        <v>40</v>
+      </c>
+      <c r="D13" s="14">
+        <v>120</v>
+      </c>
+      <c r="E13" s="14">
+        <v>30</v>
+      </c>
+      <c r="F13" s="14">
+        <v>240</v>
+      </c>
+      <c r="G13" s="14">
+        <v>4</v>
+      </c>
+      <c r="H13" s="14">
+        <v>90</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
         <v>46247</v>
       </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="B14" s="14">
+        <v>420</v>
+      </c>
+      <c r="C14" s="14">
+        <v>30</v>
+      </c>
+      <c r="D14" s="14">
+        <v>90</v>
+      </c>
+      <c r="E14" s="14">
+        <v>30</v>
+      </c>
+      <c r="F14" s="14">
+        <v>240</v>
+      </c>
+      <c r="G14" s="14">
+        <v>4</v>
+      </c>
+      <c r="H14" s="14">
+        <v>90</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13">
         <v>46248</v>
       </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="B15" s="14">
+        <v>360</v>
+      </c>
+      <c r="C15" s="14">
+        <v>0</v>
+      </c>
+      <c r="D15" s="14">
+        <v>60</v>
+      </c>
+      <c r="E15" s="14">
+        <v>0</v>
+      </c>
+      <c r="F15" s="14">
+        <v>360</v>
+      </c>
+      <c r="G15" s="14">
+        <v>6</v>
+      </c>
+      <c r="H15" s="14">
+        <v>40</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>620</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13">
         <v>46249</v>
       </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+      <c r="B16" s="14">
+        <v>480</v>
+      </c>
+      <c r="C16" s="14">
+        <v>30</v>
+      </c>
+      <c r="D16" s="14">
+        <v>90</v>
+      </c>
+      <c r="E16" s="14">
+        <v>60</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>120</v>
+      </c>
+      <c r="I16" s="15">
+        <f t="shared" ref="I16:I22" si="2">IF(SUM(B16:F16,H16)=0,"",SUM(B16:F16,H16))</f>
+        <v>780</v>
+      </c>
+      <c r="J16" s="15">
+        <f t="shared" ref="J16:J22" si="3">IF(I16="","",1440-I16)</f>
+        <v>660</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
         <v>46250</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+      <c r="B17" s="14">
+        <v>480</v>
+      </c>
+      <c r="C17" s="14">
+        <v>30</v>
+      </c>
+      <c r="D17" s="14">
+        <v>90</v>
+      </c>
+      <c r="E17" s="14">
+        <v>60</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>120</v>
+      </c>
+      <c r="I17" s="15">
+        <f t="shared" si="2"/>
+        <v>780</v>
+      </c>
+      <c r="J17" s="15">
+        <f t="shared" si="3"/>
+        <v>660</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
         <v>46251</v>
       </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+      <c r="B18" s="14">
+        <v>360</v>
+      </c>
+      <c r="C18" s="14">
+        <v>0</v>
+      </c>
+      <c r="D18" s="14">
+        <v>120</v>
+      </c>
+      <c r="E18" s="14">
+        <v>45</v>
+      </c>
+      <c r="F18" s="14">
+        <v>300</v>
+      </c>
+      <c r="G18" s="14">
+        <v>5</v>
+      </c>
+      <c r="H18" s="14">
+        <v>60</v>
+      </c>
+      <c r="I18" s="15">
+        <f t="shared" si="2"/>
+        <v>885</v>
+      </c>
+      <c r="J18" s="15">
+        <f t="shared" si="3"/>
+        <v>555</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
         <v>46252</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+      <c r="B19" s="14">
+        <v>360</v>
+      </c>
+      <c r="C19" s="14">
+        <v>45</v>
+      </c>
+      <c r="D19" s="14">
+        <v>120</v>
+      </c>
+      <c r="E19" s="14">
+        <v>30</v>
+      </c>
+      <c r="F19" s="14">
+        <v>300</v>
+      </c>
+      <c r="G19" s="14">
+        <v>5</v>
+      </c>
+      <c r="H19" s="14">
+        <v>60</v>
+      </c>
+      <c r="I19" s="15">
+        <f t="shared" si="2"/>
+        <v>915</v>
+      </c>
+      <c r="J19" s="15">
+        <f t="shared" si="3"/>
+        <v>525</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
         <v>46253</v>
       </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+      <c r="B20" s="14">
+        <v>360</v>
+      </c>
+      <c r="C20" s="14">
+        <v>40</v>
+      </c>
+      <c r="D20" s="14">
+        <v>120</v>
+      </c>
+      <c r="E20" s="14">
+        <v>30</v>
+      </c>
+      <c r="F20" s="14">
+        <v>240</v>
+      </c>
+      <c r="G20" s="14">
+        <v>4</v>
+      </c>
+      <c r="H20" s="14">
+        <v>90</v>
+      </c>
+      <c r="I20" s="15">
+        <f t="shared" si="2"/>
+        <v>880</v>
+      </c>
+      <c r="J20" s="15">
+        <f t="shared" si="3"/>
+        <v>560</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13">
         <v>46254</v>
       </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
+      <c r="C21" s="14">
+        <v>30</v>
+      </c>
+      <c r="D21" s="14">
+        <v>90</v>
+      </c>
+      <c r="E21" s="14">
+        <v>30</v>
+      </c>
+      <c r="F21" s="14">
+        <v>240</v>
+      </c>
+      <c r="G21" s="14">
+        <v>4</v>
+      </c>
+      <c r="H21" s="14">
+        <v>90</v>
+      </c>
+      <c r="I21" s="15">
+        <f t="shared" si="2"/>
+        <v>900</v>
+      </c>
+      <c r="J21" s="15">
+        <f t="shared" si="3"/>
+        <v>540</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13">
         <v>46255</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+      <c r="B22" s="14">
+        <v>360</v>
+      </c>
+      <c r="C22" s="14">
+        <v>0</v>
+      </c>
+      <c r="D22" s="14">
+        <v>60</v>
+      </c>
+      <c r="E22" s="14">
+        <v>0</v>
+      </c>
+      <c r="F22" s="14">
+        <v>360</v>
+      </c>
+      <c r="G22" s="14">
+        <v>6</v>
+      </c>
+      <c r="H22" s="14">
+        <v>40</v>
+      </c>
+      <c r="I22" s="15">
+        <f t="shared" si="2"/>
+        <v>820</v>
+      </c>
+      <c r="J22" s="15">
+        <f t="shared" si="3"/>
+        <v>620</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13">
         <v>46256</v>
       </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+      <c r="B23" s="14">
+        <v>420</v>
+      </c>
+      <c r="C23" s="14">
+        <v>30</v>
+      </c>
+      <c r="D23" s="14">
+        <v>90</v>
+      </c>
+      <c r="E23" s="14">
+        <v>60</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0</v>
+      </c>
+      <c r="G23" s="14">
+        <v>0</v>
+      </c>
+      <c r="H23" s="14">
+        <v>120</v>
+      </c>
+      <c r="I23" s="15">
+        <f t="shared" ref="I23:I29" si="4">IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
+        <v>720</v>
+      </c>
+      <c r="J23" s="15">
+        <f t="shared" ref="J23:J29" si="5">IF(I23="","",1440-I23)</f>
+        <v>720</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13">
         <v>46257</v>
       </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+      <c r="B24" s="14">
+        <v>480</v>
+      </c>
+      <c r="C24" s="14">
+        <v>30</v>
+      </c>
+      <c r="D24" s="14">
+        <v>90</v>
+      </c>
+      <c r="E24" s="14">
+        <v>60</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14">
+        <v>120</v>
+      </c>
+      <c r="I24" s="15">
+        <f t="shared" si="4"/>
+        <v>780</v>
+      </c>
+      <c r="J24" s="15">
+        <f t="shared" si="5"/>
+        <v>660</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13">
         <v>46258</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+      <c r="B25" s="14">
+        <v>360</v>
+      </c>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
+      <c r="D25" s="14">
+        <v>120</v>
+      </c>
+      <c r="E25" s="14">
+        <v>45</v>
+      </c>
+      <c r="F25" s="14">
+        <v>300</v>
+      </c>
+      <c r="G25" s="14">
+        <v>5</v>
+      </c>
+      <c r="H25" s="14">
+        <v>60</v>
+      </c>
+      <c r="I25" s="15">
+        <f t="shared" si="4"/>
+        <v>885</v>
+      </c>
+      <c r="J25" s="15">
+        <f t="shared" si="5"/>
+        <v>555</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13">
         <v>46259</v>
       </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+      <c r="B26" s="14">
+        <v>360</v>
+      </c>
+      <c r="C26" s="14">
+        <v>45</v>
+      </c>
+      <c r="D26" s="14">
+        <v>120</v>
+      </c>
+      <c r="E26" s="14">
+        <v>30</v>
+      </c>
+      <c r="F26" s="14">
+        <v>300</v>
+      </c>
+      <c r="G26" s="14">
+        <v>5</v>
+      </c>
+      <c r="H26" s="14">
+        <v>60</v>
+      </c>
+      <c r="I26" s="15">
+        <f t="shared" si="4"/>
+        <v>915</v>
+      </c>
+      <c r="J26" s="15">
+        <f t="shared" si="5"/>
+        <v>525</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="13">
         <v>46260</v>
       </c>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+      <c r="B27" s="14">
+        <v>360</v>
+      </c>
+      <c r="C27" s="14">
+        <v>40</v>
+      </c>
+      <c r="D27" s="14">
+        <v>120</v>
+      </c>
+      <c r="E27" s="14">
+        <v>30</v>
+      </c>
+      <c r="F27" s="14">
+        <v>240</v>
+      </c>
+      <c r="G27" s="14">
+        <v>4</v>
+      </c>
+      <c r="H27" s="14">
+        <v>90</v>
+      </c>
+      <c r="I27" s="15">
+        <f t="shared" si="4"/>
+        <v>880</v>
+      </c>
+      <c r="J27" s="15">
+        <f t="shared" si="5"/>
+        <v>560</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13">
         <v>46261</v>
       </c>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+      <c r="B28" s="14">
+        <v>420</v>
+      </c>
+      <c r="C28" s="14">
+        <v>30</v>
+      </c>
+      <c r="D28" s="14">
+        <v>90</v>
+      </c>
+      <c r="E28" s="14">
+        <v>30</v>
+      </c>
+      <c r="F28" s="14">
+        <v>240</v>
+      </c>
+      <c r="G28" s="14">
+        <v>4</v>
+      </c>
+      <c r="H28" s="14">
+        <v>90</v>
+      </c>
+      <c r="I28" s="15">
+        <f t="shared" si="4"/>
+        <v>900</v>
+      </c>
+      <c r="J28" s="15">
+        <f t="shared" si="5"/>
+        <v>540</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13">
         <v>46262</v>
       </c>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+      <c r="B29" s="14">
+        <v>360</v>
+      </c>
+      <c r="C29" s="14">
+        <v>0</v>
+      </c>
+      <c r="D29" s="14">
+        <v>60</v>
+      </c>
+      <c r="E29" s="14">
+        <v>0</v>
+      </c>
+      <c r="F29" s="14">
+        <v>360</v>
+      </c>
+      <c r="G29" s="14">
+        <v>6</v>
+      </c>
+      <c r="H29" s="14">
+        <v>40</v>
+      </c>
+      <c r="I29" s="15">
+        <f t="shared" si="4"/>
+        <v>820</v>
+      </c>
+      <c r="J29" s="15">
+        <f t="shared" si="5"/>
+        <v>620</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13">
         <v>46263</v>
       </c>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+      <c r="B30" s="14">
+        <v>420</v>
+      </c>
+      <c r="C30" s="14">
+        <v>30</v>
+      </c>
+      <c r="D30" s="14">
+        <v>90</v>
+      </c>
+      <c r="E30" s="14">
+        <v>60</v>
+      </c>
+      <c r="F30" s="14">
+        <v>0</v>
+      </c>
+      <c r="G30" s="14">
+        <v>0</v>
+      </c>
+      <c r="H30" s="14">
+        <v>120</v>
+      </c>
+      <c r="I30" s="15">
+        <f t="shared" ref="I30:I31" si="6">IF(SUM(B30:F30,H30)=0,"",SUM(B30:F30,H30))</f>
+        <v>720</v>
+      </c>
+      <c r="J30" s="15">
+        <f t="shared" ref="J30:J31" si="7">IF(I30="","",1440-I30)</f>
+        <v>720</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13">
         <v>46264</v>
       </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+      <c r="B31" s="14">
+        <v>480</v>
+      </c>
+      <c r="C31" s="14">
+        <v>30</v>
+      </c>
+      <c r="D31" s="14">
+        <v>90</v>
+      </c>
+      <c r="E31" s="14">
+        <v>60</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>120</v>
+      </c>
+      <c r="I31" s="15">
+        <f t="shared" si="6"/>
+        <v>780</v>
+      </c>
+      <c r="J31" s="15">
+        <f t="shared" si="7"/>
+        <v>660</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
@@ -1793,7 +2239,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="13">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
@@ -2617,11 +3063,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="8">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="9">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2639,11 +3085,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -2661,11 +3107,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -2683,11 +3129,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -2705,11 +3151,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -2727,11 +3173,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -2749,11 +3195,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -2771,11 +3217,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -2793,11 +3239,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -2815,11 +3261,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -2837,11 +3283,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -2859,11 +3305,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -2881,11 +3327,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -2903,11 +3349,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -2925,11 +3371,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -2947,11 +3393,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -2969,11 +3415,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -2991,11 +3437,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3013,11 +3459,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3035,11 +3481,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3057,11 +3503,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3079,11 +3525,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3101,11 +3547,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3123,11 +3569,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3145,11 +3591,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3167,11 +3613,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3189,11 +3635,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3211,11 +3657,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3233,11 +3679,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3255,11 +3701,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3277,11 +3723,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3299,11 +3745,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3321,11 +3767,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3343,11 +3789,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3365,11 +3811,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3387,11 +3833,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3409,11 +3855,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3431,11 +3877,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3453,11 +3899,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3475,11 +3921,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3497,11 +3943,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3519,11 +3965,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3541,11 +3987,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3563,11 +4009,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3585,11 +4031,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -3607,11 +4053,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -3629,11 +4075,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -3651,11 +4097,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -3673,11 +4119,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -3695,11 +4141,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -3717,11 +4163,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -3739,11 +4185,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -3761,11 +4207,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -3783,11 +4229,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -3805,11 +4251,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -3827,11 +4273,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -3849,11 +4295,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -3871,11 +4317,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -3893,11 +4339,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -3915,11 +4361,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -3937,11 +4383,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -3959,11 +4405,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -3981,11 +4427,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4003,11 +4449,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4025,11 +4471,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="10">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="11">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4047,11 +4493,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4069,11 +4515,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4091,11 +4537,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4113,11 +4559,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4135,11 +4581,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4157,11 +4603,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4179,11 +4625,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4201,11 +4647,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4223,11 +4669,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4245,11 +4691,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4267,11 +4713,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4289,11 +4735,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4311,11 +4757,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4333,11 +4779,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4355,11 +4801,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4377,11 +4823,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4399,11 +4845,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4421,11 +4867,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4443,11 +4889,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4465,11 +4911,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4487,11 +4933,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4509,11 +4955,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4531,11 +4977,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4553,11 +4999,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4575,11 +5021,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4597,11 +5043,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -4619,11 +5065,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -4641,11 +5087,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -4663,11 +5109,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -4685,11 +5131,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -4707,11 +5153,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -4729,11 +5175,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -4751,11 +5197,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -4773,11 +5219,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -4795,11 +5241,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -4817,11 +5263,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -4839,11 +5285,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -4861,11 +5307,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -4883,11 +5329,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -4905,11 +5351,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -4927,11 +5373,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -4949,11 +5395,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -4971,11 +5417,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -4993,11 +5439,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5015,11 +5461,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5037,11 +5483,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5059,11 +5505,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5081,11 +5527,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5103,11 +5549,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5125,11 +5571,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5147,11 +5593,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5169,11 +5615,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5191,11 +5637,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5213,11 +5659,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5235,11 +5681,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5257,11 +5703,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5279,11 +5725,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5301,11 +5747,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5323,11 +5769,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5345,11 +5791,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5367,11 +5813,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5389,11 +5835,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5411,11 +5857,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5433,11 +5879,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="12">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="13">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5455,11 +5901,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5477,11 +5923,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5499,11 +5945,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5521,11 +5967,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5543,11 +5989,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5565,11 +6011,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5587,11 +6033,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -5609,11 +6055,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -5631,11 +6077,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -5653,11 +6099,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -5675,11 +6121,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -5697,11 +6143,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -5719,11 +6165,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -5741,11 +6187,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -5763,11 +6209,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -5785,11 +6231,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -5807,11 +6253,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -5829,11 +6275,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -5851,11 +6297,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -5873,11 +6319,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -5895,11 +6341,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -5917,11 +6363,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -5939,11 +6385,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -5961,11 +6407,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -5983,11 +6429,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6005,11 +6451,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6027,11 +6473,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6049,11 +6495,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6071,11 +6517,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6093,11 +6539,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6115,11 +6561,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6137,11 +6583,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6159,11 +6605,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6181,11 +6627,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6203,11 +6649,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6225,11 +6671,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6247,11 +6693,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6269,11 +6715,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6291,11 +6737,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6313,11 +6759,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6335,11 +6781,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6357,11 +6803,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6379,11 +6825,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6401,11 +6847,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6423,11 +6869,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6445,11 +6891,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6467,11 +6913,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6489,11 +6935,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6511,11 +6957,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6533,11 +6979,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6555,11 +7001,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6577,11 +7023,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6599,11 +7045,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -6621,11 +7067,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6643,11 +7089,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6665,11 +7111,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -6687,11 +7133,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -6709,11 +7155,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -6731,11 +7177,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -6753,11 +7199,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -6775,11 +7221,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -6797,11 +7243,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -6819,11 +7265,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -6841,11 +7287,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="14">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="15">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -6863,11 +7309,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -6885,11 +7331,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -6907,11 +7353,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -6929,11 +7375,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -6951,11 +7397,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -6973,11 +7419,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -6995,11 +7441,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7017,11 +7463,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7039,11 +7485,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7061,11 +7507,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7083,11 +7529,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7105,11 +7551,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7127,11 +7573,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7149,11 +7595,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7171,11 +7617,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7193,11 +7639,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7215,11 +7661,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7237,11 +7683,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7259,11 +7705,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7281,11 +7727,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7303,11 +7749,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7325,11 +7771,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7347,11 +7793,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7369,11 +7815,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7391,11 +7837,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7413,11 +7859,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7435,11 +7881,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7457,11 +7903,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7479,11 +7925,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7501,11 +7947,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7523,11 +7969,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7545,11 +7991,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7567,11 +8013,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7589,11 +8035,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -7611,11 +8057,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -7633,11 +8079,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -7655,11 +8101,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -7677,11 +8123,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -7699,11 +8145,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -7721,11 +8167,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -7743,11 +8189,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -7765,11 +8211,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -7787,11 +8233,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -7809,11 +8255,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -7831,11 +8277,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -7853,11 +8299,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -7875,11 +8321,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -7897,11 +8343,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -7919,11 +8365,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -7941,11 +8387,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -7963,11 +8409,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -7985,11 +8431,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8007,11 +8453,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8029,11 +8475,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8051,11 +8497,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8073,11 +8519,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8095,11 +8541,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8117,11 +8563,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8139,11 +8585,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8161,11 +8607,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8183,11 +8629,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8205,11 +8651,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8227,11 +8673,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8249,11 +8695,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="16">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="17">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8271,11 +8717,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8293,11 +8739,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8315,11 +8761,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8337,11 +8783,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8359,11 +8805,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8381,11 +8827,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8403,11 +8849,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8425,11 +8871,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8447,11 +8893,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8469,11 +8915,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8491,11 +8937,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8513,11 +8959,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8535,11 +8981,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8557,11 +9003,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8579,11 +9025,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8601,11 +9047,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -8623,11 +9069,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -8645,11 +9091,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -8667,11 +9113,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -8689,11 +9135,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -8711,11 +9157,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -8733,11 +9179,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -8755,11 +9201,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -8777,11 +9223,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -8799,11 +9245,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -8821,11 +9267,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -8843,11 +9289,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -8865,11 +9311,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -8887,11 +9333,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -8909,11 +9355,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -8931,11 +9377,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -8953,11 +9399,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -8975,11 +9421,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -8997,11 +9443,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9019,11 +9465,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9041,11 +9487,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9063,11 +9509,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9085,11 +9531,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9107,11 +9553,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9129,11 +9575,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9151,11 +9597,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9173,11 +9619,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9195,11 +9641,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9217,11 +9663,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9239,11 +9685,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9261,11 +9707,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9283,11 +9729,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9305,11 +9751,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9327,11 +9773,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9349,11 +9795,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9371,11 +9817,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9393,11 +9839,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9415,11 +9861,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9437,11 +9883,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9459,11 +9905,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9481,11 +9927,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9503,11 +9949,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9525,11 +9971,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9547,11 +9993,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9569,11 +10015,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -9591,11 +10037,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -9613,11 +10059,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -9635,11 +10081,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9657,11 +10103,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="18">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="19">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9679,11 +10125,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -9701,11 +10147,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -9723,11 +10169,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -9745,11 +10191,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -9767,11 +10213,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -9789,11 +10235,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -9811,11 +10257,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -9833,11 +10279,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -9855,11 +10301,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -9877,11 +10323,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -9899,11 +10345,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/python-project.xlsx
+++ b/python-project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8CCFCF8-9715-4851-8C36-8FC66218B77C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DFC2FB8-E37C-4695-94B8-0FADBFF51622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -214,13 +214,7 @@
     <t>Neutral</t>
   </si>
   <si>
-    <t>I felt tired.</t>
-  </si>
-  <si>
     <t>felt a bit tired.</t>
-  </si>
-  <si>
-    <t>It was Saturday so no classes.</t>
   </si>
   <si>
     <t>High</t>
@@ -1065,19 +1059,19 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="13">
-        <v>46240</v>
+        <v>46247</v>
       </c>
       <c r="B7" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C7" s="14">
         <v>30</v>
       </c>
       <c r="D7" s="14">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E7" s="14">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F7" s="14">
         <v>240</v>
@@ -1086,18 +1080,18 @@
         <v>4</v>
       </c>
       <c r="H7" s="14">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="I7" s="15">
-        <f t="shared" si="0"/>
-        <v>835</v>
+        <f>IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
+        <v>900</v>
       </c>
       <c r="J7" s="15">
-        <f t="shared" si="1"/>
-        <v>605</v>
+        <f>IF(I7="","",1440-I7)</f>
+        <v>540</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="L7" s="16" t="s">
         <v>58</v>
@@ -1111,53 +1105,53 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B8" s="14">
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="C8" s="14">
         <v>0</v>
       </c>
       <c r="D8" s="14">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="E8" s="14">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F8" s="14">
-        <v>240</v>
+        <v>360</v>
       </c>
       <c r="G8" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H8" s="14">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I8" s="15">
-        <f t="shared" si="0"/>
-        <v>855</v>
+        <f>IF(SUM(B8:F8,H8)=0,"",SUM(B8:F8,H8))</f>
+        <v>820</v>
       </c>
       <c r="J8" s="15">
-        <f t="shared" si="1"/>
-        <v>585</v>
+        <f>IF(I8="","",1440-I8)</f>
+        <v>620</v>
       </c>
       <c r="K8" s="16" t="s">
         <v>58</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13">
-        <v>46242</v>
+        <v>46249</v>
       </c>
       <c r="B9" s="14">
         <v>480</v>
@@ -1181,11 +1175,11 @@
         <v>120</v>
       </c>
       <c r="I9" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I9:I15" si="2">IF(SUM(B9:F9,H9)=0,"",SUM(B9:F9,H9))</f>
         <v>780</v>
       </c>
       <c r="J9" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J9:J15" si="3">IF(I9="","",1440-I9)</f>
         <v>660</v>
       </c>
       <c r="K9" s="16" t="s">
@@ -1198,12 +1192,12 @@
         <v>51</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
-        <v>46243</v>
+        <v>46250</v>
       </c>
       <c r="B10" s="14">
         <v>480</v>
@@ -1227,11 +1221,11 @@
         <v>120</v>
       </c>
       <c r="I10" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>780</v>
       </c>
       <c r="J10" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>660</v>
       </c>
       <c r="K10" s="16" t="s">
@@ -1241,15 +1235,15 @@
         <v>50</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B11" s="14">
         <v>360</v>
@@ -1273,15 +1267,15 @@
         <v>60</v>
       </c>
       <c r="I11" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>885</v>
       </c>
       <c r="J11" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>555</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="L11" s="16" t="s">
         <v>58</v>
@@ -1290,12 +1284,12 @@
         <v>51</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="B12" s="14">
         <v>360</v>
@@ -1319,11 +1313,11 @@
         <v>60</v>
       </c>
       <c r="I12" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>915</v>
       </c>
       <c r="J12" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>525</v>
       </c>
       <c r="K12" s="16" t="s">
@@ -1333,15 +1327,15 @@
         <v>50</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
-        <v>46246</v>
+        <v>46253</v>
       </c>
       <c r="B13" s="14">
         <v>360</v>
@@ -1365,11 +1359,11 @@
         <v>90</v>
       </c>
       <c r="I13" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>880</v>
       </c>
       <c r="J13" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>560</v>
       </c>
       <c r="K13" s="16" t="s">
@@ -1382,12 +1376,12 @@
         <v>51</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="B14" s="14">
         <v>420</v>
@@ -1411,11 +1405,11 @@
         <v>90</v>
       </c>
       <c r="I14" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>900</v>
       </c>
       <c r="J14" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>540</v>
       </c>
       <c r="K14" s="16" t="s">
@@ -1428,12 +1422,12 @@
         <v>51</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B15" s="14">
         <v>360</v>
@@ -1457,11 +1451,11 @@
         <v>40</v>
       </c>
       <c r="I15" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>820</v>
       </c>
       <c r="J15" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>620</v>
       </c>
       <c r="K15" s="16" t="s">
@@ -1471,18 +1465,18 @@
         <v>50</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13">
-        <v>46249</v>
+        <v>46256</v>
       </c>
       <c r="B16" s="14">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="C16" s="14">
         <v>30</v>
@@ -1503,12 +1497,12 @@
         <v>120</v>
       </c>
       <c r="I16" s="15">
-        <f t="shared" ref="I16:I22" si="2">IF(SUM(B16:F16,H16)=0,"",SUM(B16:F16,H16))</f>
-        <v>780</v>
+        <f t="shared" ref="I16:I22" si="4">IF(SUM(B16:F16,H16)=0,"",SUM(B16:F16,H16))</f>
+        <v>720</v>
       </c>
       <c r="J16" s="15">
-        <f t="shared" ref="J16:J22" si="3">IF(I16="","",1440-I16)</f>
-        <v>660</v>
+        <f t="shared" ref="J16:J22" si="5">IF(I16="","",1440-I16)</f>
+        <v>720</v>
       </c>
       <c r="K16" s="16" t="s">
         <v>57</v>
@@ -1520,12 +1514,12 @@
         <v>51</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
-        <v>46250</v>
+        <v>46257</v>
       </c>
       <c r="B17" s="14">
         <v>480</v>
@@ -1549,11 +1543,11 @@
         <v>120</v>
       </c>
       <c r="I17" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>780</v>
       </c>
       <c r="J17" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>660</v>
       </c>
       <c r="K17" s="16" t="s">
@@ -1563,15 +1557,15 @@
         <v>50</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="B18" s="14">
         <v>360</v>
@@ -1595,15 +1589,15 @@
         <v>60</v>
       </c>
       <c r="I18" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>885</v>
       </c>
       <c r="J18" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>555</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="L18" s="16" t="s">
         <v>58</v>
@@ -1612,12 +1606,12 @@
         <v>51</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
-        <v>46252</v>
+        <v>46259</v>
       </c>
       <c r="B19" s="14">
         <v>360</v>
@@ -1641,11 +1635,11 @@
         <v>60</v>
       </c>
       <c r="I19" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>915</v>
       </c>
       <c r="J19" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>525</v>
       </c>
       <c r="K19" s="16" t="s">
@@ -1655,15 +1649,15 @@
         <v>50</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
-        <v>46253</v>
+        <v>46260</v>
       </c>
       <c r="B20" s="14">
         <v>360</v>
@@ -1687,11 +1681,11 @@
         <v>90</v>
       </c>
       <c r="I20" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>880</v>
       </c>
       <c r="J20" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>560</v>
       </c>
       <c r="K20" s="16" t="s">
@@ -1704,12 +1698,12 @@
         <v>51</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13">
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="B21" s="14">
         <v>420</v>
@@ -1733,11 +1727,11 @@
         <v>90</v>
       </c>
       <c r="I21" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>900</v>
       </c>
       <c r="J21" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>540</v>
       </c>
       <c r="K21" s="16" t="s">
@@ -1750,12 +1744,12 @@
         <v>51</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13">
-        <v>46255</v>
+        <v>46262</v>
       </c>
       <c r="B22" s="14">
         <v>360</v>
@@ -1779,11 +1773,11 @@
         <v>40</v>
       </c>
       <c r="I22" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>820</v>
       </c>
       <c r="J22" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>620</v>
       </c>
       <c r="K22" s="16" t="s">
@@ -1793,15 +1787,15 @@
         <v>50</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="B23" s="14">
         <v>420</v>
@@ -1825,11 +1819,11 @@
         <v>120</v>
       </c>
       <c r="I23" s="15">
-        <f t="shared" ref="I23:I29" si="4">IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
+        <f t="shared" ref="I23:I24" si="6">IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
         <v>720</v>
       </c>
       <c r="J23" s="15">
-        <f t="shared" ref="J23:J29" si="5">IF(I23="","",1440-I23)</f>
+        <f t="shared" ref="J23:J24" si="7">IF(I23="","",1440-I23)</f>
         <v>720</v>
       </c>
       <c r="K23" s="16" t="s">
@@ -1842,12 +1836,12 @@
         <v>51</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="B24" s="14">
         <v>480</v>
@@ -1871,11 +1865,11 @@
         <v>120</v>
       </c>
       <c r="I24" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>780</v>
       </c>
       <c r="J24" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>660</v>
       </c>
       <c r="K24" s="16" t="s">
@@ -1885,381 +1879,59 @@
         <v>50</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13">
-        <v>46258</v>
-      </c>
-      <c r="B25" s="14">
-        <v>360</v>
-      </c>
-      <c r="C25" s="14">
-        <v>0</v>
-      </c>
-      <c r="D25" s="14">
-        <v>120</v>
-      </c>
-      <c r="E25" s="14">
-        <v>45</v>
-      </c>
-      <c r="F25" s="14">
-        <v>300</v>
-      </c>
-      <c r="G25" s="14">
-        <v>5</v>
-      </c>
-      <c r="H25" s="14">
-        <v>60</v>
-      </c>
-      <c r="I25" s="15">
-        <f t="shared" si="4"/>
-        <v>885</v>
-      </c>
-      <c r="J25" s="15">
-        <f t="shared" si="5"/>
-        <v>555</v>
-      </c>
-      <c r="K25" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="L25" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M25" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N25" s="17" t="s">
-        <v>65</v>
-      </c>
+        <v>46265</v>
+      </c>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="15" t="str">
+        <f>IF(SUM(B25:F25,H25)=0,"",SUM(B25:F25,H25))</f>
+        <v/>
+      </c>
+      <c r="J25" s="15" t="str">
+        <f>IF(I25="","",1440-I25)</f>
+        <v/>
+      </c>
+      <c r="K25" s="16"/>
+      <c r="L25" s="16"/>
+      <c r="M25" s="16"/>
+      <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13">
-        <v>46259</v>
-      </c>
-      <c r="B26" s="14">
-        <v>360</v>
-      </c>
-      <c r="C26" s="14">
-        <v>45</v>
-      </c>
-      <c r="D26" s="14">
-        <v>120</v>
-      </c>
-      <c r="E26" s="14">
-        <v>30</v>
-      </c>
-      <c r="F26" s="14">
-        <v>300</v>
-      </c>
-      <c r="G26" s="14">
-        <v>5</v>
-      </c>
-      <c r="H26" s="14">
-        <v>60</v>
-      </c>
-      <c r="I26" s="15">
-        <f t="shared" si="4"/>
-        <v>915</v>
-      </c>
-      <c r="J26" s="15">
-        <f t="shared" si="5"/>
-        <v>525</v>
-      </c>
-      <c r="K26" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L26" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M26" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="N26" s="17" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13">
-        <v>46260</v>
-      </c>
-      <c r="B27" s="14">
-        <v>360</v>
-      </c>
-      <c r="C27" s="14">
-        <v>40</v>
-      </c>
-      <c r="D27" s="14">
-        <v>120</v>
-      </c>
-      <c r="E27" s="14">
-        <v>30</v>
-      </c>
-      <c r="F27" s="14">
-        <v>240</v>
-      </c>
-      <c r="G27" s="14">
-        <v>4</v>
-      </c>
-      <c r="H27" s="14">
-        <v>90</v>
-      </c>
-      <c r="I27" s="15">
-        <f t="shared" si="4"/>
-        <v>880</v>
-      </c>
-      <c r="J27" s="15">
-        <f t="shared" si="5"/>
-        <v>560</v>
-      </c>
-      <c r="K27" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="L27" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M27" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N27" s="17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13">
-        <v>46261</v>
-      </c>
-      <c r="B28" s="14">
-        <v>420</v>
-      </c>
-      <c r="C28" s="14">
-        <v>30</v>
-      </c>
-      <c r="D28" s="14">
-        <v>90</v>
-      </c>
-      <c r="E28" s="14">
-        <v>30</v>
-      </c>
-      <c r="F28" s="14">
-        <v>240</v>
-      </c>
-      <c r="G28" s="14">
-        <v>4</v>
-      </c>
-      <c r="H28" s="14">
-        <v>90</v>
-      </c>
-      <c r="I28" s="15">
-        <f t="shared" si="4"/>
-        <v>900</v>
-      </c>
-      <c r="J28" s="15">
-        <f t="shared" si="5"/>
-        <v>540</v>
-      </c>
-      <c r="K28" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L28" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M28" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N28" s="17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13">
-        <v>46262</v>
-      </c>
-      <c r="B29" s="14">
-        <v>360</v>
-      </c>
-      <c r="C29" s="14">
-        <v>0</v>
-      </c>
-      <c r="D29" s="14">
-        <v>60</v>
-      </c>
-      <c r="E29" s="14">
-        <v>0</v>
-      </c>
-      <c r="F29" s="14">
-        <v>360</v>
-      </c>
-      <c r="G29" s="14">
-        <v>6</v>
-      </c>
-      <c r="H29" s="14">
-        <v>40</v>
-      </c>
-      <c r="I29" s="15">
-        <f t="shared" si="4"/>
-        <v>820</v>
-      </c>
-      <c r="J29" s="15">
-        <f t="shared" si="5"/>
-        <v>620</v>
-      </c>
-      <c r="K29" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="L29" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M29" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="N29" s="17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13">
-        <v>46263</v>
-      </c>
-      <c r="B30" s="14">
-        <v>420</v>
-      </c>
-      <c r="C30" s="14">
-        <v>30</v>
-      </c>
-      <c r="D30" s="14">
-        <v>90</v>
-      </c>
-      <c r="E30" s="14">
-        <v>60</v>
-      </c>
-      <c r="F30" s="14">
-        <v>0</v>
-      </c>
-      <c r="G30" s="14">
-        <v>0</v>
-      </c>
-      <c r="H30" s="14">
-        <v>120</v>
-      </c>
-      <c r="I30" s="15">
-        <f t="shared" ref="I30:I31" si="6">IF(SUM(B30:F30,H30)=0,"",SUM(B30:F30,H30))</f>
-        <v>720</v>
-      </c>
-      <c r="J30" s="15">
-        <f t="shared" ref="J30:J31" si="7">IF(I30="","",1440-I30)</f>
-        <v>720</v>
-      </c>
-      <c r="K30" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L30" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M30" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N30" s="17" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13">
-        <v>46264</v>
-      </c>
-      <c r="B31" s="14">
-        <v>480</v>
-      </c>
-      <c r="C31" s="14">
-        <v>30</v>
-      </c>
-      <c r="D31" s="14">
-        <v>90</v>
-      </c>
-      <c r="E31" s="14">
-        <v>60</v>
-      </c>
-      <c r="F31" s="14">
-        <v>0</v>
-      </c>
-      <c r="G31" s="14">
-        <v>0</v>
-      </c>
-      <c r="H31" s="14">
-        <v>120</v>
-      </c>
-      <c r="I31" s="15">
-        <f t="shared" si="6"/>
-        <v>780</v>
-      </c>
-      <c r="J31" s="15">
-        <f t="shared" si="7"/>
-        <v>660</v>
-      </c>
-      <c r="K31" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L31" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M31" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="N31" s="17" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13">
-        <v>46265</v>
-      </c>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13">
         <v>46266</v>
       </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="15" t="str">
+        <f>IF(SUM(B26:F26,H26)=0,"",SUM(B26:F26,H26))</f>
+        <v/>
+      </c>
+      <c r="J26" s="15" t="str">
+        <f>IF(I26="","",1440-I26)</f>
+        <v/>
+      </c>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
+      <c r="M26" s="16"/>
+      <c r="N26" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="13"/>
@@ -10366,21 +10038,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
+  <conditionalFormatting sqref="J34:J401 J6:J26">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K34:K401 K6:K26" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L34:L401 L6:L26" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M34:M401 M6:M26" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/python-project.xlsx
+++ b/python-project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DFC2FB8-E37C-4695-94B8-0FADBFF51622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E7F315-14BE-4E98-9126-CE455C43D950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -208,22 +208,10 @@
     <t>September</t>
   </si>
   <si>
-    <t>good</t>
-  </si>
-  <si>
-    <t>Neutral</t>
-  </si>
-  <si>
     <t>felt a bit tired.</t>
   </si>
   <si>
-    <t>High</t>
-  </si>
-  <si>
     <t>It was Sunday.</t>
-  </si>
-  <si>
-    <t>Low</t>
   </si>
   <si>
     <t>It was a slow day.</t>
@@ -1090,17 +1078,17 @@
         <f>IF(I7="","",1440-I7)</f>
         <v>540</v>
       </c>
-      <c r="K7" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L7" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M7" s="16" t="s">
-        <v>51</v>
+      <c r="K7" s="16">
+        <v>4</v>
+      </c>
+      <c r="L7" s="16">
+        <v>4</v>
+      </c>
+      <c r="M7" s="16">
+        <v>4</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1136,17 +1124,17 @@
         <f>IF(I8="","",1440-I8)</f>
         <v>620</v>
       </c>
-      <c r="K8" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="L8" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M8" s="16" t="s">
-        <v>62</v>
+      <c r="K8" s="16">
+        <v>3</v>
+      </c>
+      <c r="L8" s="16">
+        <v>5</v>
+      </c>
+      <c r="M8" s="16">
+        <v>5</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1182,17 +1170,17 @@
         <f t="shared" ref="J9:J15" si="3">IF(I9="","",1440-I9)</f>
         <v>660</v>
       </c>
-      <c r="K9" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L9" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M9" s="16" t="s">
-        <v>51</v>
+      <c r="K9" s="16">
+        <v>5</v>
+      </c>
+      <c r="L9" s="16">
+        <v>4</v>
+      </c>
+      <c r="M9" s="16">
+        <v>4</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1228,17 +1216,17 @@
         <f t="shared" si="3"/>
         <v>660</v>
       </c>
-      <c r="K10" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L10" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M10" s="16" t="s">
-        <v>60</v>
+      <c r="K10" s="16">
+        <v>4</v>
+      </c>
+      <c r="L10" s="16">
+        <v>5</v>
+      </c>
+      <c r="M10" s="16">
+        <v>5</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1274,17 +1262,17 @@
         <f t="shared" si="3"/>
         <v>555</v>
       </c>
-      <c r="K11" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="L11" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M11" s="16" t="s">
-        <v>51</v>
+      <c r="K11" s="16">
+        <v>5</v>
+      </c>
+      <c r="L11" s="16">
+        <v>4</v>
+      </c>
+      <c r="M11" s="16">
+        <v>5</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1320,17 +1308,17 @@
         <f t="shared" si="3"/>
         <v>525</v>
       </c>
-      <c r="K12" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L12" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M12" s="16" t="s">
+      <c r="K12" s="16">
+        <v>5</v>
+      </c>
+      <c r="L12" s="16">
+        <v>5</v>
+      </c>
+      <c r="M12" s="16">
+        <v>5</v>
+      </c>
+      <c r="N12" s="17" t="s">
         <v>60</v>
-      </c>
-      <c r="N12" s="17" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1366,17 +1354,17 @@
         <f t="shared" si="3"/>
         <v>560</v>
       </c>
-      <c r="K13" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="L13" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M13" s="16" t="s">
-        <v>51</v>
+      <c r="K13" s="16">
+        <v>4</v>
+      </c>
+      <c r="L13" s="16">
+        <v>5</v>
+      </c>
+      <c r="M13" s="16">
+        <v>5</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1412,17 +1400,17 @@
         <f t="shared" si="3"/>
         <v>540</v>
       </c>
-      <c r="K14" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L14" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M14" s="16" t="s">
-        <v>51</v>
+      <c r="K14" s="16">
+        <v>4</v>
+      </c>
+      <c r="L14" s="16">
+        <v>5</v>
+      </c>
+      <c r="M14" s="16">
+        <v>4</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1458,17 +1446,17 @@
         <f t="shared" si="3"/>
         <v>620</v>
       </c>
-      <c r="K15" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="L15" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M15" s="16" t="s">
-        <v>62</v>
+      <c r="K15" s="16">
+        <v>5</v>
+      </c>
+      <c r="L15" s="16">
+        <v>5</v>
+      </c>
+      <c r="M15" s="16">
+        <v>5</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1504,17 +1492,17 @@
         <f t="shared" ref="J16:J22" si="5">IF(I16="","",1440-I16)</f>
         <v>720</v>
       </c>
-      <c r="K16" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L16" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M16" s="16" t="s">
-        <v>51</v>
+      <c r="K16" s="16">
+        <v>5</v>
+      </c>
+      <c r="L16" s="16">
+        <v>4</v>
+      </c>
+      <c r="M16" s="16">
+        <v>5</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1550,17 +1538,17 @@
         <f t="shared" si="5"/>
         <v>660</v>
       </c>
-      <c r="K17" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L17" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M17" s="16" t="s">
-        <v>60</v>
+      <c r="K17" s="16">
+        <v>4</v>
+      </c>
+      <c r="L17" s="16">
+        <v>4</v>
+      </c>
+      <c r="M17" s="16">
+        <v>4</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1596,17 +1584,17 @@
         <f t="shared" si="5"/>
         <v>555</v>
       </c>
-      <c r="K18" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="L18" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M18" s="16" t="s">
-        <v>51</v>
+      <c r="K18" s="16">
+        <v>5</v>
+      </c>
+      <c r="L18" s="16">
+        <v>5</v>
+      </c>
+      <c r="M18" s="16">
+        <v>5</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1642,17 +1630,17 @@
         <f t="shared" si="5"/>
         <v>525</v>
       </c>
-      <c r="K19" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L19" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M19" s="16" t="s">
+      <c r="K19" s="16">
+        <v>4</v>
+      </c>
+      <c r="L19" s="16">
+        <v>5</v>
+      </c>
+      <c r="M19" s="16">
+        <v>4</v>
+      </c>
+      <c r="N19" s="17" t="s">
         <v>60</v>
-      </c>
-      <c r="N19" s="17" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1688,17 +1676,17 @@
         <f t="shared" si="5"/>
         <v>560</v>
       </c>
-      <c r="K20" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="L20" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M20" s="16" t="s">
-        <v>51</v>
+      <c r="K20" s="16">
+        <v>4</v>
+      </c>
+      <c r="L20" s="16">
+        <v>4</v>
+      </c>
+      <c r="M20" s="16">
+        <v>5</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -1734,17 +1722,17 @@
         <f t="shared" si="5"/>
         <v>540</v>
       </c>
-      <c r="K21" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L21" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M21" s="16" t="s">
-        <v>51</v>
+      <c r="K21" s="16">
+        <v>4</v>
+      </c>
+      <c r="L21" s="16">
+        <v>4</v>
+      </c>
+      <c r="M21" s="16">
+        <v>5</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -1780,17 +1768,17 @@
         <f t="shared" si="5"/>
         <v>620</v>
       </c>
-      <c r="K22" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="L22" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M22" s="16" t="s">
-        <v>62</v>
+      <c r="K22" s="16">
+        <v>5</v>
+      </c>
+      <c r="L22" s="16">
+        <v>5</v>
+      </c>
+      <c r="M22" s="16">
+        <v>5</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -1826,17 +1814,17 @@
         <f t="shared" ref="J23:J24" si="7">IF(I23="","",1440-I23)</f>
         <v>720</v>
       </c>
-      <c r="K23" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L23" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M23" s="16" t="s">
-        <v>51</v>
+      <c r="K23" s="16">
+        <v>3</v>
+      </c>
+      <c r="L23" s="16">
+        <v>5</v>
+      </c>
+      <c r="M23" s="16">
+        <v>4</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -1872,17 +1860,17 @@
         <f t="shared" si="7"/>
         <v>660</v>
       </c>
-      <c r="K24" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L24" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M24" s="16" t="s">
-        <v>60</v>
+      <c r="K24" s="16">
+        <v>5</v>
+      </c>
+      <c r="L24" s="16">
+        <v>5</v>
+      </c>
+      <c r="M24" s="16">
+        <v>4</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
